--- a/MINI PROJECT/3IST02_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST02_Mini Project Details.xlsx
@@ -41,9 +41,6 @@
     <t>CONTACT NO</t>
   </si>
   <si>
-    <t>20241IST0065</t>
-  </si>
-  <si>
     <t>HARISH.20241IST0065@presidencyuniversity.in</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>9492549397</t>
   </si>
   <si>
-    <t>20241IST0071</t>
-  </si>
-  <si>
     <t>SARA.20241IST0071@presidencyuniversity.in</t>
   </si>
   <si>
@@ -188,9 +182,6 @@
     <t>9943401574</t>
   </si>
   <si>
-    <t>20241IST0078</t>
-  </si>
-  <si>
     <t>PALANATI.20241IST0078@presidencyuniversity.in</t>
   </si>
   <si>
@@ -218,9 +209,6 @@
     <t>9611952644</t>
   </si>
   <si>
-    <t>20241IST0081</t>
-  </si>
-  <si>
     <t>MADAN GOWDA B R</t>
   </si>
   <si>
@@ -266,9 +254,6 @@
     <t>9845769116</t>
   </si>
   <si>
-    <t>20241IST0085</t>
-  </si>
-  <si>
     <t>UMME.20241IST0085@presidencyuniversity.in</t>
   </si>
   <si>
@@ -359,9 +344,6 @@
     <t>9844071774</t>
   </si>
   <si>
-    <t>20241IST0093</t>
-  </si>
-  <si>
     <t>TALLAPANENI.20241IST0093@presidencyuniversity.in</t>
   </si>
   <si>
@@ -452,9 +434,6 @@
     <t>9140666217</t>
   </si>
   <si>
-    <t>20241IST0101</t>
-  </si>
-  <si>
     <t>SAMEEKSHA DINESH</t>
   </si>
   <si>
@@ -738,9 +717,6 @@
   </si>
   <si>
     <t>6360366425</t>
-  </si>
-  <si>
-    <t>20241IST0126</t>
   </si>
   <si>
     <t>SANIA FATHIMA S</t>
@@ -940,12 +916,36 @@
 It allows applicants to apply for jobs, upload resumes, and track status, while HR personnel can schedule interviews and manage records digitally.
 The main objective is to build a centralized HR portal that ensures efficiency, reduces paperwork, and supports transparent recruitment and employee management.</t>
   </si>
+  <si>
+    <t>20241IST0065 (lead)</t>
+  </si>
+  <si>
+    <t>20241IST0071 (lead)</t>
+  </si>
+  <si>
+    <t>20241IST0078 (Lead)</t>
+  </si>
+  <si>
+    <t>20241IST0081 (Lead)</t>
+  </si>
+  <si>
+    <t>20241IST0085 (Lead)</t>
+  </si>
+  <si>
+    <t>20241IST0093 (Lead(</t>
+  </si>
+  <si>
+    <t>20241IST0101(lead)</t>
+  </si>
+  <si>
+    <t>20241IST0126(lead)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -978,12 +978,6 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1164,38 +1158,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1502,13 +1496,13 @@
         <v>4</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
@@ -1516,26 +1510,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" s="17"/>
-      <c r="G2" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>274</v>
+      <c r="G2" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75">
@@ -1543,737 +1537,737 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" s="17"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:9" ht="15.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="17"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="28"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9" ht="15.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F5" s="17"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="28"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" ht="70.5" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="28"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" ht="15.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="I7" s="28"/>
+      <c r="G7" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9" ht="15.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="28"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" ht="15.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" s="17"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="28"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9" ht="15.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="F10" s="17"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="28"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9" ht="72.75" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F11" s="17"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="28"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9" ht="15.75">
       <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="I12" s="28"/>
+      <c r="G12" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9" ht="15.75">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F13" s="17"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="28"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9" ht="15.75">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="F14" s="17"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="28"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" ht="15.75">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F15" s="17"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="28"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" ht="89.25" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F16" s="17"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="28"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="15.75">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F17" s="17"/>
-      <c r="G17" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="I17" s="28"/>
+      <c r="G17" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9" ht="15.75">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>283</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F18" s="17"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="28"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9" ht="15.75">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="28"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" ht="15.75">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F20" s="17"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="28"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" ht="61.5" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
+      <c r="B21" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F21" s="17"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="28"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9" ht="15.75">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="I22" s="28"/>
+      <c r="G22" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9" ht="15.75">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F23" s="17"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="28"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9" ht="15.75">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="28"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9" ht="15.75">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>91</v>
+      <c r="B25" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F25" s="17"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="28"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9" ht="64.5" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="28"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9" ht="15.75">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F27" s="17"/>
-      <c r="G27" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="I27" s="28"/>
+      <c r="G27" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9" ht="15.75">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="28"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9" ht="15.75">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F29" s="17"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="28"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9" ht="15.75">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="28"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9" ht="15.75">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F31" s="17"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="28"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9" ht="35.25" customHeight="1">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F32" s="17"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="28"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="1:16" ht="15.75">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F33" s="17"/>
-      <c r="G33" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="I33" s="28"/>
+      <c r="G33" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="H33" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="1:16" ht="15.75">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F34" s="17"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="28"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:16" ht="15.75">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F35" s="17"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="28"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:16" ht="15.75">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F36" s="18"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="28"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="24"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
@@ -2287,651 +2281,646 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F37" s="17"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="28"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="1:16" ht="15.75">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F38" s="17"/>
-      <c r="G38" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="I38" s="28"/>
+      <c r="G38" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" spans="1:16" ht="15.75">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>146</v>
+      <c r="B39" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F39" s="17"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="28"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:16" ht="15.75">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F40" s="17"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="28"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:16" ht="15.75">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F41" s="17"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="28"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:16" ht="61.5" customHeight="1">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F42" s="17"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="28"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="24"/>
     </row>
     <row r="43" spans="1:16" ht="15.75">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F43" s="17"/>
-      <c r="G43" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="I43" s="28"/>
+      <c r="G43" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="1:16" ht="15.75">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F44" s="17"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="28"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="24"/>
     </row>
     <row r="45" spans="1:16" ht="15.75">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C45" s="29" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>164</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F45" s="17"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="28"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="24"/>
     </row>
     <row r="46" spans="1:16" ht="15.75">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F46" s="17"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="28"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" spans="1:16" ht="63" customHeight="1">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F47" s="17"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="28"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="1:16" ht="15.75">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F48" s="17"/>
-      <c r="G48" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="I48" s="28"/>
+      <c r="G48" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="H48" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="I48" s="24"/>
     </row>
     <row r="49" spans="1:9" ht="15.75">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="28"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="24"/>
     </row>
     <row r="50" spans="1:9" ht="15.75">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F50" s="17"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="28"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="24"/>
     </row>
     <row r="51" spans="1:9" ht="15.75">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="28"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="24"/>
     </row>
     <row r="52" spans="1:9" ht="15.75">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F52" s="17"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="28"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="24"/>
     </row>
     <row r="53" spans="1:9" ht="15.75">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F53" s="17"/>
-      <c r="G53" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="I53" s="28"/>
+      <c r="G53" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="H53" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="I53" s="24"/>
     </row>
     <row r="54" spans="1:9" ht="15.75">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F54" s="17"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="28"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="24"/>
     </row>
     <row r="55" spans="1:9" ht="15.75">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F55" s="17"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="28"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="1:9" ht="15.75">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F56" s="17"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="28"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="24"/>
     </row>
     <row r="57" spans="1:9" ht="15.75">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F57" s="17"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="28"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="24"/>
     </row>
     <row r="58" spans="1:9" ht="52.5" customHeight="1">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F58" s="17"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="28"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="24"/>
     </row>
     <row r="59" spans="1:9" ht="15.75">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F59" s="17"/>
-      <c r="G59" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="H59" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="I59" s="28"/>
+      <c r="G59" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="H59" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="I59" s="24"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C60" s="30" t="s">
-        <v>231</v>
+        <v>223</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>224</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F60" s="17"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="28"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="1:9" ht="15.75">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F61" s="17"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="28"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="1:9" ht="15.75">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C62" s="29" t="s">
-        <v>239</v>
+        <v>287</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>231</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F62" s="17"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="28"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="1:9" ht="15.75">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F63" s="19"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="28"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="24"/>
     </row>
     <row r="64" spans="1:9" ht="15.75">
       <c r="A64" s="1">
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F64" s="19"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="28"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="24"/>
     </row>
     <row r="65" spans="1:9" ht="15.75">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
       <c r="F65" s="19"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="28"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="24"/>
     </row>
     <row r="66" spans="1:9" ht="36">
       <c r="C66" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="28"/>
+        <v>254</v>
+      </c>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="24"/>
     </row>
     <row r="67" spans="1:9" ht="36">
       <c r="C67" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="28"/>
+        <v>255</v>
+      </c>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I2:I67"/>
-    <mergeCell ref="H33:H37"/>
-    <mergeCell ref="H38:H42"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="H53:H58"/>
-    <mergeCell ref="H59:H65"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="G22:G26"/>
     <mergeCell ref="G53:G58"/>
     <mergeCell ref="G59:G65"/>
     <mergeCell ref="H2:H6"/>
@@ -2948,8 +2937,13 @@
     <mergeCell ref="G2:G6"/>
     <mergeCell ref="G7:G11"/>
     <mergeCell ref="G12:G16"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="I2:I67"/>
+    <mergeCell ref="H33:H37"/>
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="H48:H52"/>
+    <mergeCell ref="H53:H58"/>
+    <mergeCell ref="H59:H65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/MINI PROJECT/3IST02_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST02_Mini Project Details.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="291">
   <si>
     <t>SI.NO</t>
   </si>
@@ -939,6 +939,15 @@
   </si>
   <si>
     <t>20241IST0126(lead)</t>
+  </si>
+  <si>
+    <t>PPT</t>
+  </si>
+  <si>
+    <t>SUBMITTED</t>
+  </si>
+  <si>
+    <t>NOT SUBMITTED</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1169,7 +1178,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1179,16 +1188,31 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1470,16 +1494,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="35.28515625" customWidth="1"/>
-    <col min="8" max="8" width="69.42578125" customWidth="1"/>
-    <col min="9" max="9" width="43.7109375" customWidth="1"/>
+    <col min="7" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="9" width="44.140625" customWidth="1"/>
+    <col min="10" max="10" width="43.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1499,13 +1523,16 @@
         <v>263</v>
       </c>
       <c r="H1" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1">
+    <row r="2" spans="1:10" ht="30" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1522,17 +1549,20 @@
         <v>6</v>
       </c>
       <c r="F2" s="17"/>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="29" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75">
+    <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1549,11 +1579,12 @@
         <v>10</v>
       </c>
       <c r="F3" s="17"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75">
+      <c r="G3" s="24"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="29"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1570,11 +1601,12 @@
         <v>14</v>
       </c>
       <c r="F4" s="17"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75">
+      <c r="G4" s="24"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="29"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1591,11 +1623,12 @@
         <v>18</v>
       </c>
       <c r="F5" s="17"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="24"/>
-    </row>
-    <row r="6" spans="1:9" ht="70.5" customHeight="1">
+      <c r="G5" s="24"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="29"/>
+    </row>
+    <row r="6" spans="1:10" ht="70.5" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1611,11 +1644,12 @@
       <c r="E6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
+      <c r="G6" s="24"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="29"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1632,15 +1666,18 @@
         <v>26</v>
       </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I7" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75">
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1657,11 +1694,12 @@
         <v>28</v>
       </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="24"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75">
+      <c r="G8" s="24"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1678,11 +1716,12 @@
         <v>31</v>
       </c>
       <c r="F9" s="17"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="24"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75">
+      <c r="G9" s="24"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1699,11 +1738,12 @@
         <v>35</v>
       </c>
       <c r="F10" s="17"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="24"/>
-    </row>
-    <row r="11" spans="1:9" ht="72.75" customHeight="1">
+      <c r="G10" s="24"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+    </row>
+    <row r="11" spans="1:10" ht="72.75" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1720,11 +1760,12 @@
         <v>39</v>
       </c>
       <c r="F11" s="17"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="24"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75">
+      <c r="G11" s="24"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -1741,15 +1782,18 @@
         <v>43</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I12" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="I12" s="24"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75">
+      <c r="J12" s="29"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1766,11 +1810,12 @@
         <v>47</v>
       </c>
       <c r="F13" s="17"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="24"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75">
+      <c r="G13" s="24"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="29"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1787,11 +1832,12 @@
         <v>51</v>
       </c>
       <c r="F14" s="17"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="24"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75">
+      <c r="G14" s="24"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="29"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1808,11 +1854,12 @@
         <v>53</v>
       </c>
       <c r="F15" s="17"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="24"/>
-    </row>
-    <row r="16" spans="1:9" ht="89.25" customHeight="1">
+      <c r="G15" s="24"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="29"/>
+    </row>
+    <row r="16" spans="1:10" ht="89.25" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1829,11 +1876,12 @@
         <v>57</v>
       </c>
       <c r="F16" s="17"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="24"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75">
+      <c r="G16" s="24"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="29"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1850,15 +1898,18 @@
         <v>60</v>
       </c>
       <c r="F17" s="17"/>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I17" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="I17" s="24"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75">
+      <c r="J17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1875,11 +1926,12 @@
         <v>63</v>
       </c>
       <c r="F18" s="17"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75">
+      <c r="G18" s="24"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="29"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1896,11 +1948,12 @@
         <v>67</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="24"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75">
+      <c r="G19" s="24"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="29"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1917,11 +1970,12 @@
         <v>71</v>
       </c>
       <c r="F20" s="17"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" ht="61.5" customHeight="1">
+      <c r="G20" s="24"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="1:10" ht="61.5" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1938,11 +1992,12 @@
         <v>75</v>
       </c>
       <c r="F21" s="17"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75">
+      <c r="G21" s="24"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1959,15 +2014,18 @@
         <v>77</v>
       </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="I22" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="I22" s="24"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75">
+      <c r="J22" s="29"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1984,11 +2042,12 @@
         <v>81</v>
       </c>
       <c r="F23" s="17"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="24"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75">
+      <c r="G23" s="24"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="29"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2005,11 +2064,12 @@
         <v>85</v>
       </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="24"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75">
+      <c r="G24" s="24"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2026,11 +2086,12 @@
         <v>89</v>
       </c>
       <c r="F25" s="17"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="24"/>
-    </row>
-    <row r="26" spans="1:9" ht="64.5" customHeight="1">
+      <c r="G25" s="24"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" ht="64.5" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2047,11 +2108,12 @@
         <v>93</v>
       </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="24"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75">
+      <c r="G26" s="24"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2068,15 +2130,18 @@
         <v>97</v>
       </c>
       <c r="F27" s="17"/>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="H27" s="25" t="s">
+      <c r="H27" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="I27" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="I27" s="24"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75">
+      <c r="J27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2093,11 +2158,12 @@
         <v>101</v>
       </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="24"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75">
+      <c r="G28" s="24"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="29"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2114,11 +2180,12 @@
         <v>105</v>
       </c>
       <c r="F29" s="17"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="24"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75">
+      <c r="G29" s="24"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2135,11 +2202,12 @@
         <v>107</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="24"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75">
+      <c r="G30" s="24"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2156,11 +2224,12 @@
         <v>111</v>
       </c>
       <c r="F31" s="17"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="24"/>
-    </row>
-    <row r="32" spans="1:9" ht="35.25" customHeight="1">
+      <c r="G31" s="24"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" ht="35.25" customHeight="1">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2177,11 +2246,12 @@
         <v>115</v>
       </c>
       <c r="F32" s="17"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="33" spans="1:16" ht="15.75">
+      <c r="G32" s="24"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="29"/>
+    </row>
+    <row r="33" spans="1:17" ht="15.75">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2198,15 +2268,18 @@
         <v>119</v>
       </c>
       <c r="F33" s="17"/>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="H33" s="25" t="s">
+      <c r="H33" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I33" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="I33" s="24"/>
-    </row>
-    <row r="34" spans="1:16" ht="15.75">
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" spans="1:17" ht="15.75">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2223,11 +2296,12 @@
         <v>123</v>
       </c>
       <c r="F34" s="17"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:16" ht="15.75">
+      <c r="G34" s="24"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="29"/>
+    </row>
+    <row r="35" spans="1:17" ht="15.75">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2244,11 +2318,12 @@
         <v>127</v>
       </c>
       <c r="F35" s="17"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="24"/>
-    </row>
-    <row r="36" spans="1:16" ht="15.75">
+      <c r="G35" s="24"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="29"/>
+    </row>
+    <row r="36" spans="1:17" ht="15.75">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2265,18 +2340,19 @@
         <v>131</v>
       </c>
       <c r="F36" s="18"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="6"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="29"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
-    </row>
-    <row r="37" spans="1:16" ht="77.25" customHeight="1">
+      <c r="Q36" s="6"/>
+    </row>
+    <row r="37" spans="1:17" ht="77.25" customHeight="1">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2293,11 +2369,12 @@
         <v>135</v>
       </c>
       <c r="F37" s="17"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="24"/>
-    </row>
-    <row r="38" spans="1:16" ht="15.75">
+      <c r="G37" s="24"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="29"/>
+    </row>
+    <row r="38" spans="1:17" ht="15.75">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2314,15 +2391,18 @@
         <v>138</v>
       </c>
       <c r="F38" s="17"/>
-      <c r="G38" s="30" t="s">
+      <c r="G38" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="H38" s="25" t="s">
+      <c r="H38" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I38" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="I38" s="24"/>
-    </row>
-    <row r="39" spans="1:16" ht="15.75">
+      <c r="J38" s="29"/>
+    </row>
+    <row r="39" spans="1:17" ht="15.75">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2339,11 +2419,12 @@
         <v>142</v>
       </c>
       <c r="F39" s="17"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="24"/>
-    </row>
-    <row r="40" spans="1:16" ht="15.75">
+      <c r="G39" s="24"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="40" spans="1:17" ht="15.75">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2360,11 +2441,12 @@
         <v>146</v>
       </c>
       <c r="F40" s="17"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="24"/>
-    </row>
-    <row r="41" spans="1:16" ht="15.75">
+      <c r="G40" s="24"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="29"/>
+    </row>
+    <row r="41" spans="1:17" ht="15.75">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2381,11 +2463,12 @@
         <v>150</v>
       </c>
       <c r="F41" s="17"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="24"/>
-    </row>
-    <row r="42" spans="1:16" ht="61.5" customHeight="1">
+      <c r="G41" s="24"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="29"/>
+    </row>
+    <row r="42" spans="1:17" ht="61.5" customHeight="1">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2402,11 +2485,12 @@
         <v>154</v>
       </c>
       <c r="F42" s="17"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="24"/>
-    </row>
-    <row r="43" spans="1:16" ht="15.75">
+      <c r="G42" s="24"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="29"/>
+    </row>
+    <row r="43" spans="1:17" ht="15.75">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2423,15 +2507,18 @@
         <v>158</v>
       </c>
       <c r="F43" s="17"/>
-      <c r="G43" s="30" t="s">
+      <c r="G43" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="H43" s="25" t="s">
+      <c r="H43" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I43" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="24"/>
-    </row>
-    <row r="44" spans="1:16" ht="15.75">
+      <c r="J43" s="29"/>
+    </row>
+    <row r="44" spans="1:17" ht="15.75">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2448,11 +2535,12 @@
         <v>162</v>
       </c>
       <c r="F44" s="17"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="24"/>
-    </row>
-    <row r="45" spans="1:16" ht="15.75">
+      <c r="G44" s="24"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="29"/>
+    </row>
+    <row r="45" spans="1:17" ht="15.75">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2469,11 +2557,12 @@
         <v>166</v>
       </c>
       <c r="F45" s="17"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="24"/>
-    </row>
-    <row r="46" spans="1:16" ht="15.75">
+      <c r="G45" s="24"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="29"/>
+    </row>
+    <row r="46" spans="1:17" ht="15.75">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -2490,11 +2579,12 @@
         <v>170</v>
       </c>
       <c r="F46" s="17"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="24"/>
-    </row>
-    <row r="47" spans="1:16" ht="63" customHeight="1">
+      <c r="G46" s="24"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="29"/>
+    </row>
+    <row r="47" spans="1:17" ht="63" customHeight="1">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2511,11 +2601,12 @@
         <v>174</v>
       </c>
       <c r="F47" s="17"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="24"/>
-    </row>
-    <row r="48" spans="1:16" ht="15.75">
+      <c r="G47" s="24"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="29"/>
+    </row>
+    <row r="48" spans="1:17" ht="15.75">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2532,15 +2623,18 @@
         <v>178</v>
       </c>
       <c r="F48" s="17"/>
-      <c r="G48" s="30" t="s">
+      <c r="G48" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="H48" s="25" t="s">
+      <c r="H48" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I48" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="I48" s="24"/>
-    </row>
-    <row r="49" spans="1:9" ht="15.75">
+      <c r="J48" s="29"/>
+    </row>
+    <row r="49" spans="1:10" ht="15.75">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2557,11 +2651,12 @@
         <v>182</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="24"/>
-    </row>
-    <row r="50" spans="1:9" ht="15.75">
+      <c r="G49" s="24"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="29"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2578,11 +2673,12 @@
         <v>186</v>
       </c>
       <c r="F50" s="17"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="24"/>
-    </row>
-    <row r="51" spans="1:9" ht="15.75">
+      <c r="G50" s="24"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="29"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.75">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2599,11 +2695,12 @@
         <v>190</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="24"/>
-    </row>
-    <row r="52" spans="1:9" ht="15.75">
+      <c r="G51" s="24"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="29"/>
+    </row>
+    <row r="52" spans="1:10" ht="15.75">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2620,11 +2717,12 @@
         <v>194</v>
       </c>
       <c r="F52" s="17"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="24"/>
-    </row>
-    <row r="53" spans="1:9" ht="15.75">
+      <c r="G52" s="24"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="29"/>
+    </row>
+    <row r="53" spans="1:10" ht="15.75">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2641,15 +2739,18 @@
         <v>198</v>
       </c>
       <c r="F53" s="17"/>
-      <c r="G53" s="27" t="s">
+      <c r="G53" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="H53" s="25" t="s">
+      <c r="H53" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="I53" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="I53" s="24"/>
-    </row>
-    <row r="54" spans="1:9" ht="15.75">
+      <c r="J53" s="29"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2666,11 +2767,12 @@
         <v>202</v>
       </c>
       <c r="F54" s="17"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="24"/>
-    </row>
-    <row r="55" spans="1:9" ht="15.75">
+      <c r="G54" s="24"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="29"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2687,11 +2789,12 @@
         <v>206</v>
       </c>
       <c r="F55" s="17"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="24"/>
-    </row>
-    <row r="56" spans="1:9" ht="15.75">
+      <c r="G55" s="24"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="29"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.75">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2708,11 +2811,12 @@
         <v>210</v>
       </c>
       <c r="F56" s="17"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="24"/>
-    </row>
-    <row r="57" spans="1:9" ht="15.75">
+      <c r="G56" s="24"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="29"/>
+    </row>
+    <row r="57" spans="1:10" ht="15.75">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2729,11 +2833,12 @@
         <v>214</v>
       </c>
       <c r="F57" s="17"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="24"/>
-    </row>
-    <row r="58" spans="1:9" ht="52.5" customHeight="1">
+      <c r="G57" s="24"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="29"/>
+    </row>
+    <row r="58" spans="1:10" ht="52.5" customHeight="1">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2750,11 +2855,12 @@
         <v>218</v>
       </c>
       <c r="F58" s="17"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="24"/>
-    </row>
-    <row r="59" spans="1:9" ht="15.75">
+      <c r="G58" s="24"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="29"/>
+    </row>
+    <row r="59" spans="1:10" ht="15.75">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2771,15 +2877,18 @@
         <v>222</v>
       </c>
       <c r="F59" s="17"/>
-      <c r="G59" s="27" t="s">
+      <c r="G59" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="H59" s="25" t="s">
+      <c r="H59" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="I59" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="I59" s="24"/>
-    </row>
-    <row r="60" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J59" s="29"/>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2796,11 +2905,12 @@
         <v>226</v>
       </c>
       <c r="F60" s="17"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="24"/>
-    </row>
-    <row r="61" spans="1:9" ht="15.75">
+      <c r="G60" s="24"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="29"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2817,11 +2927,12 @@
         <v>230</v>
       </c>
       <c r="F61" s="17"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="24"/>
-    </row>
-    <row r="62" spans="1:9" ht="15.75">
+      <c r="G61" s="24"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="29"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2838,11 +2949,12 @@
         <v>233</v>
       </c>
       <c r="F62" s="17"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="24"/>
-    </row>
-    <row r="63" spans="1:9" ht="15.75">
+      <c r="G62" s="24"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="29"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2859,11 +2971,12 @@
         <v>237</v>
       </c>
       <c r="F63" s="19"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="24"/>
-    </row>
-    <row r="64" spans="1:9" ht="15.75">
+      <c r="G63" s="24"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="29"/>
+    </row>
+    <row r="64" spans="1:10" ht="15.75">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2880,11 +2993,12 @@
         <v>241</v>
       </c>
       <c r="F64" s="19"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="24"/>
-    </row>
-    <row r="65" spans="1:9" ht="15.75">
+      <c r="G64" s="24"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="29"/>
+    </row>
+    <row r="65" spans="1:10" ht="15.75">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -2897,53 +3011,68 @@
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
       <c r="F65" s="19"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="24"/>
-    </row>
-    <row r="66" spans="1:9" ht="36">
+      <c r="G65" s="24"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="29"/>
+    </row>
+    <row r="66" spans="1:10" ht="36">
       <c r="C66" s="14" t="s">
         <v>254</v>
       </c>
       <c r="G66" s="21"/>
       <c r="H66" s="21"/>
-      <c r="I66" s="24"/>
-    </row>
-    <row r="67" spans="1:9" ht="36">
+      <c r="I66" s="21"/>
+      <c r="J66" s="29"/>
+    </row>
+    <row r="67" spans="1:10" ht="36">
       <c r="C67" s="14" t="s">
         <v>255</v>
       </c>
       <c r="G67" s="21"/>
       <c r="H67" s="21"/>
-      <c r="I67" s="24"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="37">
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="H48:H52"/>
+    <mergeCell ref="H53:H58"/>
+    <mergeCell ref="H59:H65"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="J2:J67"/>
+    <mergeCell ref="I33:I37"/>
+    <mergeCell ref="I38:I42"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="I53:I58"/>
+    <mergeCell ref="I59:I65"/>
+    <mergeCell ref="H2:H6"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="H27:H32"/>
+    <mergeCell ref="H33:H37"/>
     <mergeCell ref="G17:G21"/>
     <mergeCell ref="G22:G26"/>
     <mergeCell ref="G53:G58"/>
     <mergeCell ref="G59:G65"/>
-    <mergeCell ref="H2:H6"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="H27:H32"/>
+    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="I27:I32"/>
     <mergeCell ref="G27:G32"/>
     <mergeCell ref="G33:G37"/>
     <mergeCell ref="G38:G42"/>
     <mergeCell ref="G43:G47"/>
     <mergeCell ref="G48:G52"/>
     <mergeCell ref="G2:G6"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="I2:I67"/>
-    <mergeCell ref="H33:H37"/>
-    <mergeCell ref="H38:H42"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="H53:H58"/>
-    <mergeCell ref="H59:H65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
